--- a/histology_test.xlsx
+++ b/histology_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raynor/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA742E9-7BCF-A547-B5E4-A194FB914E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18C94D0-E41D-9044-B0C4-3A364263B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="14980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="11" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>30</v>
